--- a/03_Group_comparisons/Proteome/01_Design_Contrasts/c_data/design_contrasts_all_inputs.xlsx
+++ b/03_Group_comparisons/Proteome/01_Design_Contrasts/c_data/design_contrasts_all_inputs.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="224">
   <si>
     <t>sheet</t>
   </si>
@@ -234,31 +234,31 @@
     <t>03_Group_comparisons/Proteome/01_Design_Contrasts/T1/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>760a338b11da3351c7b746a0282b4f31</t>
+    <t>52c1ea729f95e38b647c71323efae263</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome/01_Design_Contrasts/T2/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>594f26105945a0a52521460bb8834e53</t>
+    <t>2452fe7a45dd4d8a48d453b428e4c3d1</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome/01_Design_Contrasts/T3/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>17b1703b8b2922dcaee80eca99cd4f6f</t>
+    <t>9036fd476850de1091fe54458a5a5675</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome/01_Design_Contrasts/training/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>39bad5e82d012de9e3f9d3ce95ba32c2</t>
+    <t>1104ec2e701808492db73927a3dc6ed6</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome/01_Design_Contrasts/acute/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>929e2ec3449711452fbc63d6205bd358</t>
+    <t>865b85c86830087517f2832bfbd38266</t>
   </si>
   <si>
     <t>BiocGenerics</t>
@@ -369,12 +369,24 @@
     <t>1.2.1</t>
   </si>
   <si>
+    <t>evaluate</t>
+  </si>
+  <si>
+    <t>1.0.5</t>
+  </si>
+  <si>
     <t>farver</t>
   </si>
   <si>
     <t>2.1.2</t>
   </si>
   <si>
+    <t>fastmap</t>
+  </si>
+  <si>
+    <t>1.2.0</t>
+  </si>
+  <si>
     <t>foreach</t>
   </si>
   <si>
@@ -426,6 +438,18 @@
     <t>1.1.4</t>
   </si>
   <si>
+    <t>htmltools</t>
+  </si>
+  <si>
+    <t>0.5.9</t>
+  </si>
+  <si>
+    <t>htmlwidgets</t>
+  </si>
+  <si>
+    <t>1.6.4</t>
+  </si>
+  <si>
     <t>IRanges</t>
   </si>
   <si>
@@ -438,12 +462,21 @@
     <t>1.0.14</t>
   </si>
   <si>
+    <t>jsonlite</t>
+  </si>
+  <si>
+    <t>2.0.0</t>
+  </si>
+  <si>
+    <t>knitr</t>
+  </si>
+  <si>
+    <t>1.51</t>
+  </si>
+  <si>
     <t>lifecycle</t>
   </si>
   <si>
-    <t>1.0.5</t>
-  </si>
-  <si>
     <t>limma</t>
   </si>
   <si>
@@ -468,6 +501,12 @@
     <t>1.5.0</t>
   </si>
   <si>
+    <t>otel</t>
+  </si>
+  <si>
+    <t>0.2.0</t>
+  </si>
+  <si>
     <t>pillar</t>
   </si>
   <si>
@@ -537,6 +576,12 @@
     <t>CRAN (R 4.6.1)</t>
   </si>
   <si>
+    <t>rmarkdown</t>
+  </si>
+  <si>
+    <t>2.31</t>
+  </si>
+  <si>
     <t>rprojroot</t>
   </si>
   <si>
@@ -606,6 +651,12 @@
     <t>0.5.0</t>
   </si>
   <si>
+    <t>utf8</t>
+  </si>
+  <si>
+    <t>1.2.6</t>
+  </si>
+  <si>
     <t>vctrs</t>
   </si>
   <si>
@@ -628,6 +679,12 @@
   </si>
   <si>
     <t>2.0.1</t>
+  </si>
+  <si>
+    <t>xfun</t>
+  </si>
+  <si>
+    <t>0.57</t>
   </si>
   <si>
     <t>yaml</t>
@@ -2153,7 +2210,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -2414,7 +2471,7 @@
         <v>126</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C24" t="s">
         <v>85</v>
@@ -2422,10 +2479,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B25" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C25" t="s">
         <v>85</v>
@@ -2433,10 +2490,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B26" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C26" t="s">
         <v>85</v>
@@ -2472,7 +2529,7 @@
         <v>136</v>
       </c>
       <c r="C29" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -2505,7 +2562,7 @@
         <v>142</v>
       </c>
       <c r="C32" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -2557,7 +2614,7 @@
         <v>151</v>
       </c>
       <c r="B37" t="s">
-        <v>152</v>
+        <v>117</v>
       </c>
       <c r="C37" t="s">
         <v>85</v>
@@ -2565,32 +2622,32 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
+        <v>152</v>
+      </c>
+      <c r="B38" t="s">
         <v>153</v>
       </c>
-      <c r="B38" t="s">
-        <v>154</v>
-      </c>
       <c r="C38" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
+        <v>154</v>
+      </c>
+      <c r="B39" t="s">
         <v>155</v>
       </c>
-      <c r="B39" t="s">
-        <v>156</v>
-      </c>
       <c r="C39" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
+        <v>156</v>
+      </c>
+      <c r="B40" t="s">
         <v>157</v>
-      </c>
-      <c r="B40" t="s">
-        <v>158</v>
       </c>
       <c r="C40" t="s">
         <v>85</v>
@@ -2598,10 +2655,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
+        <v>158</v>
+      </c>
+      <c r="B41" t="s">
         <v>159</v>
-      </c>
-      <c r="B41" t="s">
-        <v>160</v>
       </c>
       <c r="C41" t="s">
         <v>85</v>
@@ -2609,10 +2666,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
+        <v>160</v>
+      </c>
+      <c r="B42" t="s">
         <v>161</v>
-      </c>
-      <c r="B42" t="s">
-        <v>162</v>
       </c>
       <c r="C42" t="s">
         <v>85</v>
@@ -2620,10 +2677,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
+        <v>162</v>
+      </c>
+      <c r="B43" t="s">
         <v>163</v>
-      </c>
-      <c r="B43" t="s">
-        <v>164</v>
       </c>
       <c r="C43" t="s">
         <v>85</v>
@@ -2631,10 +2688,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
+        <v>164</v>
+      </c>
+      <c r="B44" t="s">
         <v>165</v>
-      </c>
-      <c r="B44" t="s">
-        <v>166</v>
       </c>
       <c r="C44" t="s">
         <v>85</v>
@@ -2642,10 +2699,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
+        <v>166</v>
+      </c>
+      <c r="B45" t="s">
         <v>167</v>
-      </c>
-      <c r="B45" t="s">
-        <v>168</v>
       </c>
       <c r="C45" t="s">
         <v>85</v>
@@ -2653,21 +2710,21 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
+        <v>168</v>
+      </c>
+      <c r="B46" t="s">
         <v>169</v>
       </c>
-      <c r="B46" t="s">
-        <v>170</v>
-      </c>
       <c r="C46" t="s">
-        <v>171</v>
+        <v>85</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B47" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C47" t="s">
         <v>85</v>
@@ -2675,21 +2732,21 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B48" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C48" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B49" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C49" t="s">
         <v>85</v>
@@ -2697,10 +2754,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B50" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C50" t="s">
         <v>85</v>
@@ -2708,10 +2765,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B51" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C51" t="s">
         <v>85</v>
@@ -2719,10 +2776,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B52" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C52" t="s">
         <v>85</v>
@@ -2730,21 +2787,21 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
+        <v>182</v>
+      </c>
+      <c r="B53" t="s">
+        <v>183</v>
+      </c>
+      <c r="C53" t="s">
         <v>184</v>
-      </c>
-      <c r="B53" t="s">
-        <v>185</v>
-      </c>
-      <c r="C53" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
+        <v>185</v>
+      </c>
+      <c r="B54" t="s">
         <v>186</v>
-      </c>
-      <c r="B54" t="s">
-        <v>187</v>
       </c>
       <c r="C54" t="s">
         <v>85</v>
@@ -2752,10 +2809,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
+        <v>187</v>
+      </c>
+      <c r="B55" t="s">
         <v>188</v>
-      </c>
-      <c r="B55" t="s">
-        <v>189</v>
       </c>
       <c r="C55" t="s">
         <v>85</v>
@@ -2763,21 +2820,21 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
+        <v>189</v>
+      </c>
+      <c r="B56" t="s">
         <v>190</v>
       </c>
-      <c r="B56" t="s">
-        <v>191</v>
-      </c>
       <c r="C56" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
+        <v>191</v>
+      </c>
+      <c r="B57" t="s">
         <v>192</v>
-      </c>
-      <c r="B57" t="s">
-        <v>115</v>
       </c>
       <c r="C57" t="s">
         <v>85</v>
@@ -2835,7 +2892,7 @@
         <v>202</v>
       </c>
       <c r="C62" t="s">
-        <v>171</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -2846,6 +2903,116 @@
         <v>204</v>
       </c>
       <c r="C63" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>205</v>
+      </c>
+      <c r="B64" t="s">
+        <v>206</v>
+      </c>
+      <c r="C64" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>207</v>
+      </c>
+      <c r="B65" t="s">
+        <v>115</v>
+      </c>
+      <c r="C65" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>208</v>
+      </c>
+      <c r="B66" t="s">
+        <v>209</v>
+      </c>
+      <c r="C66" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>210</v>
+      </c>
+      <c r="B67" t="s">
+        <v>211</v>
+      </c>
+      <c r="C67" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>212</v>
+      </c>
+      <c r="B68" t="s">
+        <v>213</v>
+      </c>
+      <c r="C68" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>214</v>
+      </c>
+      <c r="B69" t="s">
+        <v>215</v>
+      </c>
+      <c r="C69" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>216</v>
+      </c>
+      <c r="B70" t="s">
+        <v>217</v>
+      </c>
+      <c r="C70" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>218</v>
+      </c>
+      <c r="B71" t="s">
+        <v>219</v>
+      </c>
+      <c r="C71" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>220</v>
+      </c>
+      <c r="B72" t="s">
+        <v>221</v>
+      </c>
+      <c r="C72" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>222</v>
+      </c>
+      <c r="B73" t="s">
+        <v>223</v>
+      </c>
+      <c r="C73" t="s">
         <v>85</v>
       </c>
     </row>

--- a/03_Group_comparisons/Proteome/01_Design_Contrasts/c_data/design_contrasts_all_inputs.xlsx
+++ b/03_Group_comparisons/Proteome/01_Design_Contrasts/c_data/design_contrasts_all_inputs.xlsx
@@ -234,31 +234,31 @@
     <t>03_Group_comparisons/Proteome/01_Design_Contrasts/T1/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>52c1ea729f95e38b647c71323efae263</t>
+    <t>a76584ee8c5314e0e09f4da58f76f8ec</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome/01_Design_Contrasts/T2/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>2452fe7a45dd4d8a48d453b428e4c3d1</t>
+    <t>c02c699bec257e2782fa3b0865ebb354</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome/01_Design_Contrasts/T3/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>9036fd476850de1091fe54458a5a5675</t>
+    <t>c6ae52c0642b776b880f42492c5c816c</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome/01_Design_Contrasts/training/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>1104ec2e701808492db73927a3dc6ed6</t>
+    <t>4dcf61d4ec94ec5cd8708e6658360f27</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome/01_Design_Contrasts/acute/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>865b85c86830087517f2832bfbd38266</t>
+    <t>44d030894b1869a78135f22adcdd22ce</t>
   </si>
   <si>
     <t>BiocGenerics</t>

--- a/03_Group_comparisons/Proteome/01_Design_Contrasts/c_data/design_contrasts_all_inputs.xlsx
+++ b/03_Group_comparisons/Proteome/01_Design_Contrasts/c_data/design_contrasts_all_inputs.xlsx
@@ -234,31 +234,31 @@
     <t>03_Group_comparisons/Proteome/01_Design_Contrasts/T1/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>a76584ee8c5314e0e09f4da58f76f8ec</t>
+    <t>dffb191e7e2bc56662a28fa316115821</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome/01_Design_Contrasts/T2/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>c02c699bec257e2782fa3b0865ebb354</t>
+    <t>2086eac80332c34a730d7e09bd3c4770</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome/01_Design_Contrasts/T3/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>c6ae52c0642b776b880f42492c5c816c</t>
+    <t>70c199ff6cde75758e8f36557035b95f</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome/01_Design_Contrasts/training/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>4dcf61d4ec94ec5cd8708e6658360f27</t>
+    <t>e702ed7d1de9cb6012d8a0ab26fbd3a4</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome/01_Design_Contrasts/acute/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>44d030894b1869a78135f22adcdd22ce</t>
+    <t>9725c5080f07feb470dfb53efa43314b</t>
   </si>
   <si>
     <t>BiocGenerics</t>
